--- a/artfynd/A 20367-2025 artfynd.xlsx
+++ b/artfynd/A 20367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124799559</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rötmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>778070</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7191845</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20367-2025 artfynd.xlsx
+++ b/artfynd/A 20367-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>124671087</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>124799559</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20367-2025 artfynd.xlsx
+++ b/artfynd/A 20367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>63842495</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778371.7818999583</v>
+        <v>778372</v>
       </c>
       <c r="R2" t="n">
-        <v>7191926.273039556</v>
+        <v>7191926</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,19 +749,9 @@
           <t>2010-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,12 +782,7 @@
         <v>124671087</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,15 +876,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124799559</v>
+        <v>124671088</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,14 +907,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rötmyran, Vb</t>
+          <t>Falkliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778070</v>
+        <v>778096</v>
       </c>
       <c r="R4" t="n">
-        <v>7191845</v>
+        <v>7191916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,15 +961,527 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124671089</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Falkliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>778084</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7191928</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124799559</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rötmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>778070</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7191845</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125013936</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>778058</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7191907</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125014012</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>778079</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7191921</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125014041</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>778113</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7191912</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20367-2025 artfynd.xlsx
+++ b/artfynd/A 20367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63842495</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124671087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124671088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124671089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1164,6 +1189,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124799559</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125013936</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125014012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,8 +1522,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125014041</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>